--- a/4_pagos/efectivo/trazabilidad/trazabilidad_2026-06.xlsx
+++ b/4_pagos/efectivo/trazabilidad/trazabilidad_2026-06.xlsx
@@ -751,7 +751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,104 @@
       </c>
       <c r="K8" s="15" t="n">
         <v>46185.68578923611</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>mesa_1</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Wilder Trujillo</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>113</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>46179</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>46186.46313923415</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>mesa_2</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Yerald Romero</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>46178</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>46186.46313923415</v>
       </c>
     </row>
   </sheetData>

--- a/4_pagos/efectivo/trazabilidad/trazabilidad_2026-06.xlsx
+++ b/4_pagos/efectivo/trazabilidad/trazabilidad_2026-06.xlsx
@@ -1191,7 +1191,7 @@
         <v>4</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>46186.46313923415</v>
+        <v>46186.46313923611</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -1240,7 +1240,7 @@
         <v>4</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>46186.46313923415</v>
+        <v>46186.46313923611</v>
       </c>
     </row>
   </sheetData>

--- a/4_pagos/efectivo/trazabilidad/trazabilidad_2026-06.xlsx
+++ b/4_pagos/efectivo/trazabilidad/trazabilidad_2026-06.xlsx
@@ -854,12 +854,12 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>BLANCO</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>BLANCO</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -1001,13 +1001,11 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>16</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -1050,7 +1048,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
